--- a/data/reports/Kiem dinh CLAUDE BOT 2026-10-24.xlsx
+++ b/data/reports/Kiem dinh CLAUDE BOT 2026-10-24.xlsx
@@ -517,7 +517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BÁO CÁO KIỂM ĐỊNH CLAUDE BOT V1 &amp; V2 – 16:02 24/10/2026</t>
+          <t>BÁO CÁO KIỂM ĐỊNH CLAUDE BOT V1 &amp; V2 – 16:13 24/10/2026</t>
         </is>
       </c>
     </row>
